--- a/app/assets/estimate-template.xlsx
+++ b/app/assets/estimate-template.xlsx
@@ -60983,9 +60983,6 @@
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.25"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;LParts: 816.600.5801&amp;CDirect: 816.600.5852&amp;REmail: ghart@controlservice.com</oddFooter>
-  </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
